--- a/datasets/commission_formation/data/output/commissioners.xlsx
+++ b/datasets/commission_formation/data/output/commissioners.xlsx
@@ -568,12 +568,12 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/97a0c3eb-8554-4a00-80de-4e35cc0d5dbd_en?filename=Mission%20letter%20-%20ALBUQUERQUE.pdf</t>
+          <t>https://commission.europa.eu/document/download/ac06a896-2645-4857-9958-467d2ce6f221_en?filename=Mission+letter+-+ALBUQUERQUE.pdf</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>2024-11-11</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -645,12 +645,12 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/4b0c6a80-adf5-4622-97ff-1f3e0ca3f7c9_en?filename=Mission%20letter%20-%20BRUNNER.pdf</t>
+          <t>https://commission.europa.eu/document/download/ea79c47b-22f8-4390-a119-5115dc40fc3e_en?filename=Mission+letter+-+BRUNNER.pdf</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -722,12 +722,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/6c5bd45b-1027-44b7-8e52-5e0c0f7a2db2_en?filename=Mission%20letter%20-%20DOMBROVSKIS.pdf</t>
+          <t>https://commission.europa.eu/document/download/71c3190f-0886-4202-846e-5750f188f116_en?filename=Mission+letter+-+DOMBROVSKIS.pdf</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -799,7 +799,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/2fcf318a-447b-4469-8e0c-302989f1d0af_en?filename=Mission%20letter%20-%20FITTO.pdf</t>
+          <t>https://commission.europa.eu/document/download/1bf50cbe-45a4-4dc5-9922-52c6c2d3959f_en?filename=Mission+letter+-+FITTO.pdf</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -876,12 +876,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/71b2b6e2-bdd4-4a5a-b6ea-b2c9f0d7a3e5_en?filename=Mission%20letter%20-%20HANSEN.pdf</t>
+          <t>https://commission.europa.eu/document/download/2c64e540-c07a-4376-a1da-368d289f4afe_en?filename=Mission+letter+-+HANSEN.pdf</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -953,12 +953,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/e409928c-ca86-459e-b7a5-e4aecf547638_en?filename=Mission%20letter%20-%20HOEKSTRA.pdf</t>
+          <t>https://commission.europa.eu/document/download/27658b9f-f1f8-4e3a-b265-1ccbd7c2af82_en?filename=Mission+letter+-+HOEKSTRA.pdf</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -1030,7 +1030,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/2fbd2d43-2cb1-4cf3-870c-60e2f7c1bf42_en?filename=Mission%20letter%20-%20JORGENSEN.pdf</t>
+          <t>https://commission.europa.eu/document/download/1c203799-0137-482e-bd18-4f6813535986_en?filename=Mission+letter+-+JORGENSEN.pdf</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>EPP</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>DISY</t>
+          <t>Independent</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1107,7 +1107,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/f47bbb5e-ee53-4ada-8df0-68f3f5e6a169_en?filename=Mission%20letter%20-%20KADIS.pdf</t>
+          <t>https://commission.europa.eu/document/download/028ce7d5-e328-4416-8f0d-35c8884acaa8_en?filename=Mission+letter+-+KADIS.pdf</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1184,12 +1184,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/2390b896-74c4-4cbd-84c3-1d3e25ae840b_en?filename=Mission%20letter%20-%20KALLAS.pdf</t>
+          <t>https://commission.europa.eu/document/download/1fd85a66-b89a-492b-8855-89499106c1d4_en?filename=Mission+letter+-+KALLAS.pdf</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1261,12 +1261,12 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/a0be6bae-3276-430a-8c7a-b2099bd0c5eb_en?filename=Mission%20letter%20-%20KOS.pdf</t>
+          <t>https://commission.europa.eu/document/download/1a2d0ad0-270d-441b-98c8-b6be364d8272_en?filename=Mission+letter+-+KOS.pdf</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/33e0c5c7-7c2b-4820-a89e-51c9e6fa009e_en?filename=Mission%20letter%20-%20KUBILIUS.pdf</t>
+          <t>https://commission.europa.eu/document/download/1f8ec030-d018-41a2-9759-c694d4d56d6c_en?filename=Mission+letter+-+KUBILIUS.pdf</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1415,12 +1415,12 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/d23edab0-a0db-433d-93f2-08e6c3e03faf_en?filename=Mission%20letter%20-%20LAHBIB.pdf</t>
+          <t>https://commission.europa.eu/document/download/faaf33ff-c8c7-49a1-b01d-56681e11a5e6_en?filename=Mission+letter+-+LAHBIB.pdf</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1492,12 +1492,12 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/54e06ec4-d7f3-426b-871d-60b52e56c528_en?filename=Mission%20letter%20-%20MCGRATH.pdf</t>
+          <t>https://commission.europa.eu/document/download/907fd6b6-0474-47d7-99da-47007ca30d02_en?filename=Mission+letter+-+McGRATH.pdf</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="O14" t="inlineStr">
@@ -1569,12 +1569,12 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/4fc0c83f-c3d5-4e83-a26f-db2e9c976fed_en?filename=Mission%20letter%20-%20MICALLEF.pdf</t>
+          <t>https://commission.europa.eu/document/download/c8b8682b-ca47-461b-bc95-c98195919eb0_en?filename=Mission+letter+-+MICALLEF.pdf</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1646,12 +1646,12 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/16c93eca-57f0-42d1-88e7-2cb64f3f5e41_en?filename=Mission%20letter%20-%20MINZATU.pdf</t>
+          <t>https://commission.europa.eu/document/download/27ac73de-6b5c-430d-8504-a76b634d5f2d_en?filename=Mission+letter+-+MINZATU.pdf</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1723,7 +1723,7 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/d7aab4e0-5c06-4e4b-be85-41a9e7e1e984_en?filename=Mission%20letter%20-%20RIBERA.pdf</t>
+          <t>https://commission.europa.eu/document/download/5b1aaee5-681f-470b-9fd5-aee14e106196_en?filename=Mission+letter+-+RIBERA.pdf</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
@@ -1800,12 +1800,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/d5d0b42c-fca4-4e92-8c8d-6d9e99f8c712_en?filename=Mission%20letter%20-%20ROSWALL.pdf</t>
+          <t>https://commission.europa.eu/document/download/10a1fd18-2f1b-4363-828e-bb72851ffce1_en?filename=Mission+letter+-+ROSWALL.pdf</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1877,12 +1877,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/80e4a22d-9a79-4c18-8d73-7dd383339c80_en?filename=Mission%20letter%20-%20SERAFIN.pdf</t>
+          <t>https://commission.europa.eu/document/download/db369caa-19e7-4560-96e0-37dc2556f676_en?filename=Mission+letter+-+SERAFIN.pdf</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-07</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1954,12 +1954,12 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/6e0c51c2-890a-4a58-9f28-2b920d44dd6d_en?filename=Mission%20letter%20-%20SEJOURNE.pdf</t>
+          <t>https://commission.europa.eu/document/download/6ef52679-19b9-4a8d-b7b2-cb99eb384eca_en?filename=Mission+letter+-+SEJOURNE.pdf</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/2d48e977-d3e5-43de-a6a2-b43ed0538992_en?filename=Mission%20letter%20-%20SIKELA.pdf</t>
+          <t>https://commission.europa.eu/document/download/6ead2cb7-41e2-454e-b7c8-5ab3707d07dd_en?filename=Mission+letter+-+SIKELA.pdf</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
         <is>
-          <t>2024-11-05</t>
+          <t>2024-11-06</t>
         </is>
       </c>
       <c r="O21" t="inlineStr">
@@ -2108,12 +2108,12 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/e2dc8f7e-c7f7-49a3-a22a-4b3f4b4a49e4_en?filename=Mission%20letter%20-%20TZITZIKOSTAS.pdf</t>
+          <t>https://commission.europa.eu/document/download/de676935-f28c-41c1-bbd2-e54646c82941_en?filename=Mission+letter+-+TZITZIKOSTAS.pdf</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
         <is>
-          <t>2024-11-06</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="O22" t="inlineStr">
@@ -2185,12 +2185,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/e409928c-ca86-459e-b7a5-e4aecf547638_en?filename=Mission%20letter%20-%20VIRKKUNEN.pdf</t>
+          <t>https://commission.europa.eu/document/download/3b537594-9264-4249-a912-5b102b7b49a3_en?filename=Mission+letter+-+VIRKKUNEN.pdf</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>2024-11-04</t>
+          <t>2024-11-12</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2262,7 +2262,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/a44bef3b-5e81-4161-a661-16a5d97a807f_en?filename=Mission%20letter%20-%20VARHELYI.pdf</t>
+          <t>https://commission.europa.eu/document/download/b1817a1b-e62e-4949-bbb8-ebf29b54c8bd_en?filename=Mission+letter+-+VARHELYI.pdf</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2339,12 +2339,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/e9d36b01-9d7f-407a-84b5-bc2e6bfda96a_en?filename=Mission%20letter%20-%20ZAHARIEVA.pdf</t>
+          <t>https://commission.europa.eu/document/download/130e9159-8616-4c29-9f61-04592557cf4c_en?filename=Mission+letter+-+ZAHARIEVA.pdf</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>2024-11-07</t>
+          <t>2024-11-05</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2485,7 +2485,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/3669ab9f-a269-4ced-b5fd-ab6a1a0d7a74_en?filename=Mission%20letter%20-%20SEFCOVIC.pdf</t>
+          <t>https://commission.europa.eu/document/download/4047c277-f608-48d1-8800-dcf0405d76e8_en?filename=Mission+letter+-+SEFCOVIC.pdf</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2562,7 +2562,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>https://commission.europa.eu/document/download/be48e2ec-22d7-439a-a625-948cccb39ef1_en?filename=Mission%20letter%20-%20SUICA.pdf</t>
+          <t>https://commission.europa.eu/document/download/24039223-f92e-40a0-a440-a27d9715051a_en?filename=Mission+letter+-+SUICA.pdf</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
